--- a/ageing_2025.xlsx
+++ b/ageing_2025.xlsx
@@ -12,129 +12,48 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t xml:space="preserve"/>
   </si>
   <si>
-    <t xml:space="preserve">三ヶ日町上尾奈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町津々崎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町佐久米</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町大谷</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町釣</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町都筑</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町三ヶ日</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町平山</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町只木</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町大崎</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町駒場</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町本坂</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町宇志</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町岡本</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町下尾奈</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町福長</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町日比沢</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町摩訶耶</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日町鵺代</t>
-  </si>
-  <si>
-    <t xml:space="preserve">三ヶ日地区</t>
+    <t xml:space="preserve">新都田五丁目）@</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新都田二丁目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新都田三丁目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新都田一丁目</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新都田四丁目）*</t>
+  </si>
+  <si>
+    <t xml:space="preserve">新都田地区</t>
   </si>
   <si>
     <t xml:space="preserve">高齢化率</t>
   </si>
   <si>
-    <t xml:space="preserve">44.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">43%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">40.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">39.3%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38.9%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.7%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">36.2%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">35.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">34.8%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">31.4%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">29.6%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">28.5%</t>
-  </si>
-  <si>
-    <t xml:space="preserve">38%</t>
+    <t xml:space="preserve">23.3%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NaN%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NA%</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.3%</t>
   </si>
 </sst>
 </file>
@@ -485,112 +404,28 @@
       <c r="G1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>16</v>
-      </c>
-      <c r="R1" t="s">
-        <v>17</v>
-      </c>
-      <c r="S1" t="s">
-        <v>18</v>
-      </c>
-      <c r="T1" t="s">
-        <v>19</v>
-      </c>
-      <c r="U1" t="s">
-        <v>20</v>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>21</v>
+        <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>10</v>
       </c>
       <c r="E2" t="s">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F2" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="G2" t="s">
-        <v>26</v>
-      </c>
-      <c r="H2" t="s">
-        <v>27</v>
-      </c>
-      <c r="I2" t="s">
-        <v>28</v>
-      </c>
-      <c r="J2" t="s">
-        <v>29</v>
-      </c>
-      <c r="K2" t="s">
-        <v>30</v>
-      </c>
-      <c r="L2" t="s">
-        <v>31</v>
-      </c>
-      <c r="M2" t="s">
-        <v>32</v>
-      </c>
-      <c r="N2" t="s">
-        <v>33</v>
-      </c>
-      <c r="O2" t="s">
-        <v>34</v>
-      </c>
-      <c r="P2" t="s">
-        <v>35</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>36</v>
-      </c>
-      <c r="R2" t="s">
-        <v>37</v>
-      </c>
-      <c r="S2" t="s">
-        <v>38</v>
-      </c>
-      <c r="T2" t="s">
-        <v>39</v>
-      </c>
-      <c r="U2" t="s">
-        <v>40</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
